--- a/data/trans_dic/IP1010-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen trastonos mentales</t>
+          <t>Menores que padecen trastonos mentales (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,37</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,92</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,29</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,83</t>
+          <t>0,49; 4,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,72</t>
+          <t>0,21; 1,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,31</t>
+          <t>0,24; 2,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,54</t>
+          <t>0,26; 2,36</t>
         </is>
       </c>
     </row>
@@ -787,32 +788,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,79</t>
+          <t>0,0; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,51</t>
+          <t>0,0; 1,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,11</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -822,12 +823,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,93</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,11</t>
+          <t>0,43; 3,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,02</t>
+          <t>0,22; 1,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,81</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,5</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,28</t>
+          <t>0,15; 1,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 1,0</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,0</t>
+          <t>0,0; 0,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,44</t>
+          <t>0,0; 0,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,36</t>
+          <t>0,28; 1,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,8</t>
+          <t>0,09; 0,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,38</t>
+          <t>0,29; 1,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,76</t>
+          <t>0,19; 0,75</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,63</t>
+          <t>0,14; 0,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,76</t>
+          <t>0,18; 0,75</t>
         </is>
       </c>
     </row>
@@ -1182,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen trastonos mentales (tasa de respuesta: 99,76%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1652</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1881</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2339</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3469</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5767</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3981</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3452</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>730; 7163</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>601; 5067</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>688; 6417</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>729; 6644</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1309</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3218</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3341</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4646</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4586</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4547</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2256</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2644</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>642; 5386</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>642; 5471</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2646</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2610</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3526</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5185</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4486</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4208</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>624; 5891</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4111</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>5905</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>4744</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>5581</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4323</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5962</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2983</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2014; 9275</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>688; 6731</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2179; 10137</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2635; 10560</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1991; 9159</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2643; 10800</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1010-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Habitat-trans_dic.xlsx
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,32 +693,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,84</t>
+          <t>0,49; 4,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,74</t>
+          <t>0,21; 1,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,22</t>
+          <t>0,24; 2,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,36</t>
+          <t>0,26; 2,58</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,65</t>
+          <t>0,0; 1,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -813,12 +813,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,07</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,13</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,05</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
     </row>
@@ -903,17 +903,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,46</t>
+          <t>0,0; 1,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,6</t>
+          <t>0,43; 3,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,9</t>
+          <t>0,22; 1,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
     </row>
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,7</t>
+          <t>0,0; 1,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,5</t>
+          <t>0,3; 2,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,41</t>
+          <t>0,15; 1,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,0</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,64</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,84</t>
+          <t>0,06; 0,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,42</t>
+          <t>0,0; 0,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,28</t>
+          <t>0,28; 1,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,9</t>
+          <t>0,09; 0,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,36</t>
+          <t>0,29; 1,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,75</t>
+          <t>0,19; 0,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,63</t>
+          <t>0,14; 0,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,75</t>
+          <t>0,18; 0,7</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3469</t>
+          <t>0; 2459</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5767</t>
+          <t>0; 6233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1432,32 +1432,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3981</t>
+          <t>0; 3961</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3452</t>
+          <t>0; 4101</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>730; 7163</t>
+          <t>719; 6570</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>601; 5067</t>
+          <t>599; 5608</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>688; 6417</t>
+          <t>686; 6821</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>729; 6644</t>
+          <t>726; 7280</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3697</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3341</t>
+          <t>0; 3340</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 4646</t>
+          <t>0; 4600</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4586</t>
+          <t>0; 3947</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4179</t>
         </is>
       </c>
     </row>
@@ -1748,17 +1748,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2256</t>
+          <t>0; 2037</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2644</t>
+          <t>0; 2985</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>642; 5386</t>
+          <t>640; 5583</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1773,17 +1773,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>642; 5471</t>
+          <t>641; 5420</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2646</t>
+          <t>0; 2478</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 2610</t>
+          <t>0; 3066</t>
         </is>
       </c>
     </row>
@@ -1921,32 +1921,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3526</t>
+          <t>0; 3955</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5185</t>
+          <t>623; 5315</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4486</t>
+          <t>0; 4112</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4208</t>
+          <t>0; 3921</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>624; 5891</t>
+          <t>623; 5335</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4111</t>
+          <t>0; 4108</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4323</t>
+          <t>0; 4360</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5962</t>
+          <t>443; 6428</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2983</t>
+          <t>0; 2598</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2014; 9275</t>
+          <t>2007; 9933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>688; 6731</t>
+          <t>686; 6345</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2179; 10137</t>
+          <t>2171; 10557</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2635; 10560</t>
+          <t>2718; 10625</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1991; 9159</t>
+          <t>1965; 9590</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2643; 10800</t>
+          <t>2558; 10088</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1010-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP1010-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,96%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,0; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,49; 4,83</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,48</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 4,37</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,59</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,68</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,49; 4,44</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,92</t>
+          <t>0,21; 1,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,36</t>
+          <t>0,24; 2,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,58</t>
+          <t>0,26; 2,54</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,89</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,27 +798,27 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0,0; 2,11</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,79</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,57</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,05</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 1,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,0; 0,93</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0,43; 4,11</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,32</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,73</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,89</t>
+          <t>0,22; 2,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,05</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,37 +1008,37 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 1,69</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,3; 2,5</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,25</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 1,9</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,3; 2,57</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,0</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,94</t>
+          <t>0,0; 0,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,8</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,18%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1118,32 +1118,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0,28; 1,36</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0,29; 1,38</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>0,06; 0,91</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,37</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0,28; 1,37</t>
-        </is>
-      </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,85</t>
+          <t>0,06; 1,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,42</t>
+          <t>0,0; 0,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,66</t>
+          <t>0,12; 0,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,7</t>
+          <t>0,18; 0,76</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1275</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2905</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>605</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>1652</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1275</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2905</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2459</t>
+          <t>0; 4469</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 6233</t>
+          <t>0; 3509</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>730; 7150</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3441</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5954</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3961</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 4101</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>719; 6570</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>599; 5608</t>
+          <t>600; 5019</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>686; 6821</t>
+          <t>689; 6701</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>726; 7280</t>
+          <t>726; 7169</t>
         </is>
       </c>
     </row>
@@ -1484,22 +1484,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3697</t>
+          <t>0; 3195</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1590,27 +1590,27 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0; 4736</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3499</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3340</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 4600</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3947</t>
+          <t>0; 4606</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4179</t>
+          <t>0; 4017</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>443</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>642; 6144</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0; 2037</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 2985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>640; 5583</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2181</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2617</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>641; 5420</t>
+          <t>641; 5810</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2478</t>
+          <t>0; 2211</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3066</t>
+          <t>0; 3394</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1962</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>818</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>0; 3517</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>623; 5182</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4638</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0; 3955</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>623; 5315</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>0; 4112</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3921</t>
+          <t>0; 3534</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>623; 5335</t>
+          <t>622; 5323</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4108</t>
+          <t>0; 3294</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>4658</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2649</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5057</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>1247</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>2095</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>524</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4658</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2649</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>5057</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4360</t>
+          <t>2006; 9829</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>443; 6428</t>
+          <t>650; 6022</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 2598</t>
+          <t>2192; 10311</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2007; 9933</t>
+          <t>0; 4377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>686; 6345</t>
+          <t>443; 7101</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2171; 10557</t>
+          <t>0; 3127</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2718; 10625</t>
+          <t>2702; 10642</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1965; 9590</t>
+          <t>1772; 9189</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2558; 10088</t>
+          <t>2663; 11001</t>
         </is>
       </c>
     </row>
